--- a/design/Справочные таблицы/Элементы.xlsx
+++ b/design/Справочные таблицы/Элементы.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="110">
   <si>
     <t>Сила</t>
   </si>
@@ -101,9 +101,6 @@
     <t>Дружелюбие?</t>
   </si>
   <si>
-    <t>Атрибут роста имеет в т.ч параметр занимаемой площади</t>
-  </si>
-  <si>
     <t>Травма</t>
   </si>
   <si>
@@ -336,6 +333,21 @@
   </si>
   <si>
     <t>Активный уворот</t>
+  </si>
+  <si>
+    <t>От атрибута роста зависит в т.ч параметр занимаемой площади и тени.</t>
+  </si>
+  <si>
+    <t>От этого атрибута зависит, где сможет разместиться юнит; куда он может пройти.</t>
+  </si>
+  <si>
+    <t>Зависит, сколько клеток юнит прикрывает своим телом (эффективность как укрытия).</t>
+  </si>
+  <si>
+    <t>Прикрытие (cover)</t>
+  </si>
+  <si>
+    <t>Площадь</t>
   </si>
 </sst>
 </file>
@@ -757,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -766,7 +778,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>25</v>
@@ -777,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -856,7 +868,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -919,42 +931,58 @@
     </row>
     <row r="27" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>96</v>
+    </row>
+    <row r="32" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -976,50 +1004,50 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
         <v>72</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1040,21 +1068,21 @@
   <sheetData>
     <row r="1" spans="1:3" s="8" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="12" customFormat="1" ht="90.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C2" s="11">
         <v>1</v>
@@ -1062,7 +1090,7 @@
     </row>
     <row r="3" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11">
@@ -1071,7 +1099,7 @@
     </row>
     <row r="4" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11">
@@ -1080,7 +1108,7 @@
     </row>
     <row r="5" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11">
@@ -1089,7 +1117,7 @@
     </row>
     <row r="6" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11">
@@ -1098,7 +1126,7 @@
     </row>
     <row r="7" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11">
@@ -1107,10 +1135,10 @@
     </row>
     <row r="8" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>42</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>43</v>
       </c>
       <c r="C8" s="9">
         <v>2</v>
@@ -1118,7 +1146,7 @@
     </row>
     <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="9">
         <v>2</v>
@@ -1126,7 +1154,7 @@
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="9">
         <v>2</v>
@@ -1134,7 +1162,7 @@
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="9">
         <v>2</v>
@@ -1142,7 +1170,7 @@
     </row>
     <row r="12" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11">
@@ -1151,7 +1179,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="9">
         <v>2</v>
@@ -1159,10 +1187,10 @@
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>50</v>
       </c>
       <c r="C14" s="9">
         <v>2</v>
@@ -1170,10 +1198,10 @@
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C15" s="9">
         <v>2</v>
@@ -1181,10 +1209,10 @@
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" s="9">
         <v>2</v>
@@ -1192,10 +1220,10 @@
     </row>
     <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" s="9">
         <v>2</v>
@@ -1203,7 +1231,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="9">
         <v>2</v>
@@ -1211,10 +1239,10 @@
     </row>
     <row r="19" spans="1:3" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>56</v>
       </c>
       <c r="C19" s="11">
         <v>1</v>
@@ -1222,10 +1250,10 @@
     </row>
     <row r="20" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>58</v>
       </c>
       <c r="C20" s="11">
         <v>1</v>
@@ -1233,7 +1261,7 @@
     </row>
     <row r="21" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11">
@@ -1242,7 +1270,7 @@
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22" s="9">
         <v>2</v>
@@ -1250,7 +1278,7 @@
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23" s="9">
         <v>2</v>
@@ -1258,10 +1286,10 @@
     </row>
     <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>64</v>
       </c>
       <c r="C24" s="9">
         <v>2</v>
@@ -1269,10 +1297,10 @@
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="C25" s="9">
         <v>2</v>
@@ -1280,10 +1308,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C26" s="9">
         <v>2</v>
@@ -1291,7 +1319,7 @@
     </row>
     <row r="27" spans="1:3" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11">
@@ -1300,7 +1328,7 @@
     </row>
     <row r="28" spans="1:3" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11">
@@ -1309,7 +1337,7 @@
     </row>
     <row r="29" spans="1:3" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11">
@@ -1318,7 +1346,7 @@
     </row>
     <row r="30" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11">
@@ -1327,7 +1355,7 @@
     </row>
     <row r="31" spans="1:3" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11">
@@ -1336,7 +1364,7 @@
     </row>
     <row r="32" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11">
@@ -1345,7 +1373,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1365,38 +1393,38 @@
   <sheetData>
     <row r="1" spans="1:2" s="7" customFormat="1" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1417,35 +1445,35 @@
   <sheetData>
     <row r="1" spans="1:3" s="7" customFormat="1" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="61.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
